--- a/AdditionalUniqueNPC/package/LangMod/JP/Dialog/Drama/mc_aun_misalie.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/Dialog/Drama/mc_aun_misalie.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="213">
   <si>
     <t>step</t>
   </si>
@@ -351,7 +351,7 @@
   </si>
   <si>
     <t xml:space="preserve">すごい…マナが…溢れ出てくる…！ こんな艶やかなマナ…見ているだけで…わたしの身体が熱く…なりそう…だ…。
-…今…全部すすって…やるからな…。</t>
+…気持ちいいのか？ わたしが…全部すすって…やるからな…。</t>
   </si>
   <si>
     <t>1.2</t>
@@ -366,6 +366,9 @@
     <t>drink</t>
   </si>
   <si>
+    <t>mc_aun_drain_mana_pc(0.2)</t>
+  </si>
+  <si>
     <t>mod_affinity(20)</t>
   </si>
   <si>
@@ -381,7 +384,7 @@
     <t>89</t>
   </si>
   <si>
-    <t xml:space="preserve">…気分はどうだ？ 痛いところはないか？ 普段よりはかなり弱く、なるべく気持ちよくなれるようにしたつもりだが…。その…嫌じゃなかったら…嬉しい。
+    <t xml:space="preserve">…気分はどうだ？ 痛いところはないか？ 普段よりはかなり弱く、なるべく気持ちよくなれるようにしたつもりだが…。その…嫌じゃなかったら…いいな…。
 ん？ マナを吸われている時、変な顔になっていなかったかって？ ああ、それに関しては何も言わないでおくよ。</t>
   </si>
   <si>
@@ -916,14 +919,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3025,61 +3028,61 @@
       <c r="K99" s="34"/>
     </row>
     <row r="100" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="35"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="37"/>
-      <c r="D100" s="37"/>
-      <c r="E100" s="35"/>
-      <c r="F100" s="35"/>
-      <c r="G100" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="H100" s="35" t="s">
+      <c r="A100" s="31"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="33"/>
+      <c r="D100" s="33"/>
+      <c r="E100" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="I100" s="38" t="s">
+      <c r="G100" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H100" s="31"/>
+      <c r="I100" s="34"/>
+      <c r="J100" s="34"/>
+      <c r="K100" s="34"/>
+    </row>
+    <row r="101" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="35"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="37"/>
+      <c r="D101" s="37"/>
+      <c r="E101" s="35"/>
+      <c r="F101" s="35"/>
+      <c r="G101" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="H101" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="J100" s="38"/>
-      <c r="K100" s="38"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="31"/>
-      <c r="B101" s="32"/>
-      <c r="C101" s="33"/>
-      <c r="D101" s="33"/>
-      <c r="E101" s="31" t="s">
+      <c r="I101" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="J101" s="38"/>
+      <c r="K101" s="38"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="31"/>
+      <c r="B102" s="32"/>
+      <c r="C102" s="33"/>
+      <c r="D102" s="33"/>
+      <c r="E102" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="F101" s="31" t="s">
+      <c r="F102" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="G101" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="H101" s="31"/>
-      <c r="I101" s="34"/>
-      <c r="J101" s="34"/>
-      <c r="K101" s="34"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="35"/>
-      <c r="B102" s="36"/>
-      <c r="C102" s="37"/>
-      <c r="D102" s="37"/>
-      <c r="E102" s="35"/>
-      <c r="F102" s="35"/>
-      <c r="G102" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="H102" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="I102" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="J102" s="38"/>
-      <c r="K102" s="38"/>
+      <c r="G102" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H102" s="31"/>
+      <c r="I102" s="34"/>
+      <c r="J102" s="34"/>
+      <c r="K102" s="34"/>
     </row>
     <row r="103" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
@@ -3089,27 +3092,33 @@
       <c r="E103" s="35"/>
       <c r="F103" s="35"/>
       <c r="G103" s="35" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H103" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="I103" s="38" t="s">
         <v>119</v>
-      </c>
-      <c r="I103" s="38" t="s">
-        <v>53</v>
       </c>
       <c r="J103" s="38"/>
       <c r="K103" s="38"/>
     </row>
     <row r="104" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
-      <c r="B104" s="35"/>
-      <c r="C104" s="35"/>
-      <c r="D104" s="35"/>
+      <c r="B104" s="36"/>
+      <c r="C104" s="37"/>
+      <c r="D104" s="37"/>
       <c r="E104" s="35"/>
       <c r="F104" s="35"/>
-      <c r="G104" s="35"/>
-      <c r="H104" s="35"/>
-      <c r="I104" s="38"/>
+      <c r="G104" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H104" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I104" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="J104" s="38"/>
       <c r="K104" s="38"/>
     </row>
@@ -3128,84 +3137,84 @@
     </row>
     <row r="106" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="39"/>
-      <c r="B106" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="C106" s="41"/>
-      <c r="D106" s="41"/>
+      <c r="B106" s="39"/>
+      <c r="C106" s="39"/>
+      <c r="D106" s="39"/>
       <c r="E106" s="39"/>
       <c r="F106" s="39"/>
       <c r="G106" s="39"/>
       <c r="H106" s="39"/>
-      <c r="I106" s="42"/>
-      <c r="J106" s="42"/>
-      <c r="K106" s="42"/>
+      <c r="I106" s="40"/>
+      <c r="J106" s="40"/>
+      <c r="K106" s="40"/>
     </row>
     <row r="107" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="43" t="s">
+      <c r="A107" s="39"/>
+      <c r="B107" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C107" s="42"/>
+      <c r="D107" s="42"/>
+      <c r="E107" s="39"/>
+      <c r="F107" s="39"/>
+      <c r="G107" s="39"/>
+      <c r="H107" s="39"/>
+      <c r="I107" s="40"/>
+      <c r="J107" s="40"/>
+      <c r="K107" s="40"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="B107" s="44"/>
-      <c r="C107" s="45"/>
-      <c r="D107" s="45"/>
-      <c r="E107" s="43"/>
-      <c r="F107" s="43"/>
-      <c r="G107" s="43"/>
-      <c r="H107" s="43"/>
-      <c r="I107" s="46"/>
-      <c r="J107" s="46"/>
-      <c r="K107" s="46"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="47"/>
-      <c r="B108" s="48"/>
-      <c r="C108" s="49"/>
-      <c r="D108" s="49"/>
-      <c r="E108" s="47" t="s">
+      <c r="B108" s="44"/>
+      <c r="C108" s="45"/>
+      <c r="D108" s="45"/>
+      <c r="E108" s="43"/>
+      <c r="F108" s="43"/>
+      <c r="G108" s="43"/>
+      <c r="H108" s="43"/>
+      <c r="I108" s="46"/>
+      <c r="J108" s="46"/>
+      <c r="K108" s="46"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" s="47"/>
+      <c r="B109" s="48"/>
+      <c r="C109" s="49"/>
+      <c r="D109" s="49"/>
+      <c r="E109" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F108" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="G108" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H108" s="47"/>
-      <c r="I108" s="50"/>
-      <c r="J108" s="50"/>
-      <c r="K108" s="50"/>
-    </row>
-    <row r="109" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="39"/>
-      <c r="B109" s="40"/>
-      <c r="C109" s="41"/>
-      <c r="D109" s="41"/>
-      <c r="E109" s="39"/>
-      <c r="F109" s="39"/>
-      <c r="G109" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H109" s="39" t="s">
+      <c r="F109" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="I109" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="J109" s="42"/>
-      <c r="K109" s="42"/>
+      <c r="G109" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H109" s="47"/>
+      <c r="I109" s="50"/>
+      <c r="J109" s="50"/>
+      <c r="K109" s="50"/>
     </row>
     <row r="110" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="39"/>
-      <c r="B110" s="39"/>
-      <c r="C110" s="39"/>
-      <c r="D110" s="39"/>
+      <c r="B110" s="41"/>
+      <c r="C110" s="42"/>
+      <c r="D110" s="42"/>
       <c r="E110" s="39"/>
       <c r="F110" s="39"/>
-      <c r="G110" s="39"/>
-      <c r="H110" s="39"/>
-      <c r="I110" s="42"/>
-      <c r="J110" s="42"/>
-      <c r="K110" s="42"/>
+      <c r="G110" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="I110" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="J110" s="40"/>
+      <c r="K110" s="40"/>
     </row>
     <row r="111" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="39"/>
@@ -3216,194 +3225,186 @@
       <c r="F111" s="39"/>
       <c r="G111" s="39"/>
       <c r="H111" s="39"/>
-      <c r="I111" s="42"/>
-      <c r="J111" s="42"/>
-      <c r="K111" s="42"/>
+      <c r="I111" s="40"/>
+      <c r="J111" s="40"/>
+      <c r="K111" s="40"/>
     </row>
     <row r="112" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="39"/>
-      <c r="B112" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="C112" s="41"/>
-      <c r="D112" s="41"/>
+      <c r="B112" s="39"/>
+      <c r="C112" s="39"/>
+      <c r="D112" s="39"/>
       <c r="E112" s="39"/>
       <c r="F112" s="39"/>
       <c r="G112" s="39"/>
       <c r="H112" s="39"/>
-      <c r="I112" s="42"/>
-      <c r="J112" s="42"/>
-      <c r="K112" s="42"/>
+      <c r="I112" s="40"/>
+      <c r="J112" s="40"/>
+      <c r="K112" s="40"/>
     </row>
     <row r="113" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B113" s="44"/>
-      <c r="C113" s="45"/>
-      <c r="D113" s="45"/>
-      <c r="E113" s="43"/>
-      <c r="F113" s="43"/>
-      <c r="G113" s="43"/>
-      <c r="H113" s="43"/>
-      <c r="I113" s="46"/>
-      <c r="J113" s="46"/>
-      <c r="K113" s="46"/>
+      <c r="A113" s="39"/>
+      <c r="B113" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C113" s="42"/>
+      <c r="D113" s="42"/>
+      <c r="E113" s="39"/>
+      <c r="F113" s="39"/>
+      <c r="G113" s="39"/>
+      <c r="H113" s="39"/>
+      <c r="I113" s="40"/>
+      <c r="J113" s="40"/>
+      <c r="K113" s="40"/>
     </row>
     <row r="114" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="47"/>
-      <c r="B114" s="48"/>
-      <c r="C114" s="49"/>
-      <c r="D114" s="49"/>
-      <c r="E114" s="47" t="s">
+      <c r="A114" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="B114" s="44"/>
+      <c r="C114" s="45"/>
+      <c r="D114" s="45"/>
+      <c r="E114" s="43"/>
+      <c r="F114" s="43"/>
+      <c r="G114" s="43"/>
+      <c r="H114" s="43"/>
+      <c r="I114" s="46"/>
+      <c r="J114" s="46"/>
+      <c r="K114" s="46"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="47"/>
+      <c r="B115" s="48"/>
+      <c r="C115" s="49"/>
+      <c r="D115" s="49"/>
+      <c r="E115" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F114" s="47" t="s">
+      <c r="F115" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="G114" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H114" s="47"/>
-      <c r="I114" s="50"/>
-      <c r="J114" s="50"/>
-      <c r="K114" s="50"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="39"/>
-      <c r="B115" s="40"/>
-      <c r="C115" s="41"/>
-      <c r="D115" s="41"/>
-      <c r="E115" s="39"/>
-      <c r="F115" s="39"/>
-      <c r="G115" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H115" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="I115" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="J115" s="42"/>
-      <c r="K115" s="42"/>
+      <c r="G115" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H115" s="47"/>
+      <c r="I115" s="50"/>
+      <c r="J115" s="50"/>
+      <c r="K115" s="50"/>
     </row>
     <row r="116" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="39"/>
-      <c r="B116" s="40"/>
-      <c r="C116" s="41"/>
-      <c r="D116" s="41"/>
+      <c r="B116" s="41"/>
+      <c r="C116" s="42"/>
+      <c r="D116" s="42"/>
       <c r="E116" s="39"/>
       <c r="F116" s="39"/>
       <c r="G116" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H116" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="I116" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="J116" s="40"/>
+      <c r="K116" s="40"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="39"/>
+      <c r="B117" s="41"/>
+      <c r="C117" s="42"/>
+      <c r="D117" s="42"/>
+      <c r="E117" s="39"/>
+      <c r="F117" s="39"/>
+      <c r="G117" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="H116" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="I116" s="42" t="s">
+      <c r="H117" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="J116" s="42"/>
-      <c r="K116" s="42"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="47"/>
-      <c r="B117" s="48"/>
-      <c r="C117" s="49"/>
-      <c r="D117" s="49"/>
-      <c r="E117" s="47" t="s">
+      <c r="I117" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="J117" s="40"/>
+      <c r="K117" s="40"/>
+    </row>
+    <row r="118" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" s="47"/>
+      <c r="B118" s="48"/>
+      <c r="C118" s="49"/>
+      <c r="D118" s="49"/>
+      <c r="E118" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F117" s="47" t="s">
+      <c r="F118" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="G117" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H117" s="47"/>
-      <c r="I117" s="50"/>
-      <c r="J117" s="50"/>
-      <c r="K117" s="50"/>
-    </row>
-    <row r="118" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="39"/>
-      <c r="B118" s="40"/>
-      <c r="C118" s="41"/>
-      <c r="D118" s="41"/>
-      <c r="E118" s="39"/>
-      <c r="F118" s="39"/>
-      <c r="G118" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H118" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="I118" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="J118" s="42"/>
-      <c r="K118" s="42"/>
+      <c r="G118" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H118" s="47"/>
+      <c r="I118" s="50"/>
+      <c r="J118" s="50"/>
+      <c r="K118" s="50"/>
     </row>
     <row r="119" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="39"/>
-      <c r="B119" s="40"/>
-      <c r="C119" s="41"/>
-      <c r="D119" s="41"/>
+      <c r="B119" s="41"/>
+      <c r="C119" s="42"/>
+      <c r="D119" s="42"/>
       <c r="E119" s="39"/>
       <c r="F119" s="39"/>
       <c r="G119" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H119" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="I119" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="J119" s="40"/>
+      <c r="K119" s="40"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" s="39"/>
+      <c r="B120" s="41"/>
+      <c r="C120" s="42"/>
+      <c r="D120" s="42"/>
+      <c r="E120" s="39"/>
+      <c r="F120" s="39"/>
+      <c r="G120" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="H119" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="I119" s="42" t="s">
+      <c r="H120" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="J119" s="42"/>
-      <c r="K119" s="42"/>
-    </row>
-    <row r="120" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="51"/>
-      <c r="B120" s="52"/>
-      <c r="C120" s="53"/>
-      <c r="D120" s="53"/>
-      <c r="E120" s="51" t="s">
+      <c r="I120" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="J120" s="40"/>
+      <c r="K120" s="40"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="51"/>
+      <c r="B121" s="52"/>
+      <c r="C121" s="53"/>
+      <c r="D121" s="53"/>
+      <c r="E121" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F120" s="51"/>
-      <c r="G120" s="51"/>
-      <c r="H120" s="51"/>
-      <c r="I120" s="54"/>
-      <c r="J120" s="54"/>
-      <c r="K120" s="54"/>
-    </row>
-    <row r="121" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="55"/>
-      <c r="B121" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C121" s="57"/>
-      <c r="D121" s="57"/>
-      <c r="E121" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="F121" s="55"/>
-      <c r="G121" s="55"/>
-      <c r="H121" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="I121" s="58" t="s">
-        <v>134</v>
-      </c>
-      <c r="J121" s="58"/>
-      <c r="K121" s="58"/>
+      <c r="F121" s="51"/>
+      <c r="G121" s="51"/>
+      <c r="H121" s="51"/>
+      <c r="I121" s="54"/>
+      <c r="J121" s="54"/>
+      <c r="K121" s="54"/>
     </row>
     <row r="122" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="55"/>
       <c r="B122" s="56" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C122" s="57"/>
       <c r="D122" s="57"/>
@@ -3413,43 +3414,51 @@
       <c r="F122" s="55"/>
       <c r="G122" s="55"/>
       <c r="H122" s="55" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I122" s="58" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J122" s="58"/>
       <c r="K122" s="58"/>
     </row>
     <row r="123" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="59"/>
-      <c r="B123" s="60" t="s">
+      <c r="A123" s="55"/>
+      <c r="B123" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C123" s="57"/>
+      <c r="D123" s="57"/>
+      <c r="E123" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="F123" s="55"/>
+      <c r="G123" s="55"/>
+      <c r="H123" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="I123" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="J123" s="58"/>
+      <c r="K123" s="58"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="59"/>
+      <c r="B124" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="C123" s="61"/>
-      <c r="D123" s="61"/>
-      <c r="E123" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="F123" s="59"/>
-      <c r="G123" s="59"/>
-      <c r="H123" s="59"/>
-      <c r="I123" s="62"/>
-      <c r="J123" s="62"/>
-      <c r="K123" s="62"/>
-    </row>
-    <row r="124" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="39"/>
-      <c r="B124" s="39"/>
-      <c r="C124" s="39"/>
-      <c r="D124" s="39"/>
-      <c r="E124" s="39"/>
-      <c r="F124" s="39"/>
-      <c r="G124" s="39"/>
-      <c r="H124" s="39"/>
-      <c r="I124" s="42"/>
-      <c r="J124" s="42"/>
-      <c r="K124" s="42"/>
+      <c r="C124" s="61"/>
+      <c r="D124" s="61"/>
+      <c r="E124" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="F124" s="59"/>
+      <c r="G124" s="59"/>
+      <c r="H124" s="59"/>
+      <c r="I124" s="62"/>
+      <c r="J124" s="62"/>
+      <c r="K124" s="62"/>
     </row>
     <row r="125" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="39"/>
@@ -3460,100 +3469,94 @@
       <c r="F125" s="39"/>
       <c r="G125" s="39"/>
       <c r="H125" s="39"/>
-      <c r="I125" s="42"/>
-      <c r="J125" s="42"/>
-      <c r="K125" s="42"/>
+      <c r="I125" s="40"/>
+      <c r="J125" s="40"/>
+      <c r="K125" s="40"/>
     </row>
     <row r="126" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="B126" s="44"/>
-      <c r="C126" s="45"/>
-      <c r="D126" s="45"/>
-      <c r="E126" s="43"/>
-      <c r="F126" s="43"/>
-      <c r="G126" s="43"/>
-      <c r="H126" s="43"/>
-      <c r="I126" s="46"/>
-      <c r="J126" s="46"/>
-      <c r="K126" s="46"/>
+      <c r="A126" s="39"/>
+      <c r="B126" s="39"/>
+      <c r="C126" s="39"/>
+      <c r="D126" s="39"/>
+      <c r="E126" s="39"/>
+      <c r="F126" s="39"/>
+      <c r="G126" s="39"/>
+      <c r="H126" s="39"/>
+      <c r="I126" s="40"/>
+      <c r="J126" s="40"/>
+      <c r="K126" s="40"/>
     </row>
     <row r="127" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" s="47"/>
-      <c r="B127" s="48"/>
-      <c r="C127" s="49"/>
-      <c r="D127" s="49"/>
-      <c r="E127" s="47" t="s">
+      <c r="A127" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" s="44"/>
+      <c r="C127" s="45"/>
+      <c r="D127" s="45"/>
+      <c r="E127" s="43"/>
+      <c r="F127" s="43"/>
+      <c r="G127" s="43"/>
+      <c r="H127" s="43"/>
+      <c r="I127" s="46"/>
+      <c r="J127" s="46"/>
+      <c r="K127" s="46"/>
+    </row>
+    <row r="128" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="47"/>
+      <c r="B128" s="48"/>
+      <c r="C128" s="49"/>
+      <c r="D128" s="49"/>
+      <c r="E128" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F127" s="47" t="s">
+      <c r="F128" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="G127" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H127" s="47"/>
-      <c r="I127" s="50"/>
-      <c r="J127" s="50"/>
-      <c r="K127" s="50"/>
-    </row>
-    <row r="128" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" s="39"/>
-      <c r="B128" s="40"/>
-      <c r="C128" s="41"/>
-      <c r="D128" s="41"/>
-      <c r="E128" s="39"/>
-      <c r="F128" s="39"/>
-      <c r="G128" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H128" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I128" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="J128" s="42"/>
-      <c r="K128" s="42"/>
+      <c r="G128" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H128" s="47"/>
+      <c r="I128" s="50"/>
+      <c r="J128" s="50"/>
+      <c r="K128" s="50"/>
     </row>
     <row r="129" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="39"/>
-      <c r="B129" s="40"/>
-      <c r="C129" s="41"/>
-      <c r="D129" s="41"/>
+      <c r="B129" s="41"/>
+      <c r="C129" s="42"/>
+      <c r="D129" s="42"/>
       <c r="E129" s="39"/>
       <c r="F129" s="39"/>
       <c r="G129" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H129" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="I129" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="J129" s="40"/>
+      <c r="K129" s="40"/>
+    </row>
+    <row r="130" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" s="39"/>
+      <c r="B130" s="41"/>
+      <c r="C130" s="42"/>
+      <c r="D130" s="42"/>
+      <c r="E130" s="39"/>
+      <c r="F130" s="39"/>
+      <c r="G130" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="H129" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="I129" s="42" t="s">
+      <c r="H130" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="J129" s="42"/>
-      <c r="K129" s="42"/>
-    </row>
-    <row r="130" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A130" s="47"/>
-      <c r="B130" s="48"/>
-      <c r="C130" s="49"/>
-      <c r="D130" s="49"/>
-      <c r="E130" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F130" s="47" t="s">
+      <c r="I130" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="G130" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H130" s="47"/>
-      <c r="I130" s="50"/>
-      <c r="J130" s="50"/>
-      <c r="K130" s="50"/>
+      <c r="J130" s="40"/>
+      <c r="K130" s="40"/>
     </row>
     <row r="131" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="47"/>
@@ -3586,7 +3589,7 @@
         <v>145</v>
       </c>
       <c r="G132" s="47" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H132" s="47"/>
       <c r="I132" s="50"/>
@@ -3594,47 +3597,53 @@
       <c r="K132" s="50"/>
     </row>
     <row r="133" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A133" s="63"/>
-      <c r="B133" s="64"/>
-      <c r="C133" s="65"/>
-      <c r="D133" s="65"/>
-      <c r="E133" s="63" t="s">
+      <c r="A133" s="47"/>
+      <c r="B133" s="48"/>
+      <c r="C133" s="49"/>
+      <c r="D133" s="49"/>
+      <c r="E133" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="F133" s="63"/>
-      <c r="G133" s="63"/>
-      <c r="H133" s="63"/>
-      <c r="I133" s="66"/>
-      <c r="J133" s="66"/>
-      <c r="K133" s="66"/>
+      <c r="G133" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="H133" s="47"/>
+      <c r="I133" s="50"/>
+      <c r="J133" s="50"/>
+      <c r="K133" s="50"/>
     </row>
     <row r="134" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A134" s="51"/>
-      <c r="B134" s="52"/>
-      <c r="C134" s="53"/>
-      <c r="D134" s="53"/>
-      <c r="E134" s="51" t="s">
+      <c r="A134" s="63"/>
+      <c r="B134" s="64"/>
+      <c r="C134" s="65"/>
+      <c r="D134" s="65"/>
+      <c r="E134" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="F134" s="63"/>
+      <c r="G134" s="63"/>
+      <c r="H134" s="63"/>
+      <c r="I134" s="66"/>
+      <c r="J134" s="66"/>
+      <c r="K134" s="66"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="51"/>
+      <c r="B135" s="52"/>
+      <c r="C135" s="53"/>
+      <c r="D135" s="53"/>
+      <c r="E135" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F134" s="51"/>
-      <c r="G134" s="51"/>
-      <c r="H134" s="51"/>
-      <c r="I134" s="54"/>
-      <c r="J134" s="54"/>
-      <c r="K134" s="54"/>
-    </row>
-    <row r="135" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" s="39"/>
-      <c r="B135" s="39"/>
-      <c r="C135" s="39"/>
-      <c r="D135" s="39"/>
-      <c r="E135" s="39"/>
-      <c r="F135" s="39"/>
-      <c r="G135" s="39"/>
-      <c r="H135" s="39"/>
-      <c r="I135" s="42"/>
-      <c r="J135" s="42"/>
-      <c r="K135" s="42"/>
+      <c r="F135" s="51"/>
+      <c r="G135" s="51"/>
+      <c r="H135" s="51"/>
+      <c r="I135" s="54"/>
+      <c r="J135" s="54"/>
+      <c r="K135" s="54"/>
     </row>
     <row r="136" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="39"/>
@@ -3645,143 +3654,143 @@
       <c r="F136" s="39"/>
       <c r="G136" s="39"/>
       <c r="H136" s="39"/>
-      <c r="I136" s="42"/>
-      <c r="J136" s="42"/>
-      <c r="K136" s="42"/>
+      <c r="I136" s="40"/>
+      <c r="J136" s="40"/>
+      <c r="K136" s="40"/>
     </row>
     <row r="137" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="B137" s="44"/>
-      <c r="C137" s="45"/>
-      <c r="D137" s="45"/>
-      <c r="E137" s="43"/>
-      <c r="F137" s="43"/>
-      <c r="G137" s="43"/>
-      <c r="H137" s="43"/>
-      <c r="I137" s="46"/>
-      <c r="J137" s="46"/>
-      <c r="K137" s="46"/>
+      <c r="A137" s="39"/>
+      <c r="B137" s="39"/>
+      <c r="C137" s="39"/>
+      <c r="D137" s="39"/>
+      <c r="E137" s="39"/>
+      <c r="F137" s="39"/>
+      <c r="G137" s="39"/>
+      <c r="H137" s="39"/>
+      <c r="I137" s="40"/>
+      <c r="J137" s="40"/>
+      <c r="K137" s="40"/>
     </row>
     <row r="138" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" s="47"/>
-      <c r="B138" s="48"/>
-      <c r="C138" s="49"/>
-      <c r="D138" s="49"/>
-      <c r="E138" s="47" t="s">
+      <c r="A138" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138" s="44"/>
+      <c r="C138" s="45"/>
+      <c r="D138" s="45"/>
+      <c r="E138" s="43"/>
+      <c r="F138" s="43"/>
+      <c r="G138" s="43"/>
+      <c r="H138" s="43"/>
+      <c r="I138" s="46"/>
+      <c r="J138" s="46"/>
+      <c r="K138" s="46"/>
+    </row>
+    <row r="139" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" s="47"/>
+      <c r="B139" s="48"/>
+      <c r="C139" s="49"/>
+      <c r="D139" s="49"/>
+      <c r="E139" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F138" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="G138" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H138" s="47"/>
-      <c r="I138" s="50"/>
-      <c r="J138" s="50"/>
-      <c r="K138" s="50"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139" s="39"/>
-      <c r="B139" s="40"/>
-      <c r="C139" s="41"/>
-      <c r="D139" s="41"/>
-      <c r="E139" s="39"/>
-      <c r="F139" s="39"/>
-      <c r="G139" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H139" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="I139" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="J139" s="42"/>
-      <c r="K139" s="42"/>
+      <c r="F139" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G139" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H139" s="47"/>
+      <c r="I139" s="50"/>
+      <c r="J139" s="50"/>
+      <c r="K139" s="50"/>
     </row>
     <row r="140" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="39"/>
-      <c r="B140" s="40"/>
-      <c r="C140" s="41"/>
-      <c r="D140" s="41"/>
+      <c r="B140" s="41"/>
+      <c r="C140" s="42"/>
+      <c r="D140" s="42"/>
       <c r="E140" s="39"/>
       <c r="F140" s="39"/>
       <c r="G140" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H140" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="I140" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="J140" s="40"/>
+      <c r="K140" s="40"/>
+    </row>
+    <row r="141" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" s="39"/>
+      <c r="B141" s="41"/>
+      <c r="C141" s="42"/>
+      <c r="D141" s="42"/>
+      <c r="E141" s="39"/>
+      <c r="F141" s="39"/>
+      <c r="G141" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="H140" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="I140" s="42" t="s">
+      <c r="H141" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="J140" s="42"/>
-      <c r="K140" s="42"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A141" s="47"/>
-      <c r="B141" s="48"/>
-      <c r="C141" s="49"/>
-      <c r="D141" s="49"/>
-      <c r="E141" s="47" t="s">
+      <c r="I141" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="J141" s="40"/>
+      <c r="K141" s="40"/>
+    </row>
+    <row r="142" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" s="47"/>
+      <c r="B142" s="48"/>
+      <c r="C142" s="49"/>
+      <c r="D142" s="49"/>
+      <c r="E142" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F141" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="G141" s="47" t="s">
+      <c r="F142" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="G142" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="H141" s="47"/>
-      <c r="I141" s="50"/>
-      <c r="J141" s="50"/>
-      <c r="K141" s="50"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A142" s="63"/>
-      <c r="B142" s="64"/>
-      <c r="C142" s="65"/>
-      <c r="D142" s="65"/>
-      <c r="E142" s="63" t="s">
-        <v>146</v>
-      </c>
-      <c r="F142" s="63"/>
-      <c r="G142" s="63"/>
-      <c r="H142" s="63"/>
-      <c r="I142" s="66"/>
-      <c r="J142" s="66"/>
-      <c r="K142" s="66"/>
+      <c r="H142" s="47"/>
+      <c r="I142" s="50"/>
+      <c r="J142" s="50"/>
+      <c r="K142" s="50"/>
     </row>
     <row r="143" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A143" s="51"/>
-      <c r="B143" s="52"/>
-      <c r="C143" s="53"/>
-      <c r="D143" s="53"/>
-      <c r="E143" s="51" t="s">
+      <c r="A143" s="63"/>
+      <c r="B143" s="64"/>
+      <c r="C143" s="65"/>
+      <c r="D143" s="65"/>
+      <c r="E143" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="F143" s="63"/>
+      <c r="G143" s="63"/>
+      <c r="H143" s="63"/>
+      <c r="I143" s="66"/>
+      <c r="J143" s="66"/>
+      <c r="K143" s="66"/>
+    </row>
+    <row r="144" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" s="51"/>
+      <c r="B144" s="52"/>
+      <c r="C144" s="53"/>
+      <c r="D144" s="53"/>
+      <c r="E144" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F143" s="51"/>
-      <c r="G143" s="51"/>
-      <c r="H143" s="51"/>
-      <c r="I143" s="54"/>
-      <c r="J143" s="54"/>
-      <c r="K143" s="54"/>
-    </row>
-    <row r="144" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" s="39"/>
-      <c r="B144" s="39"/>
-      <c r="C144" s="39"/>
-      <c r="D144" s="39"/>
-      <c r="E144" s="39"/>
-      <c r="F144" s="39"/>
-      <c r="G144" s="39"/>
-      <c r="H144" s="39"/>
-      <c r="I144" s="42"/>
-      <c r="J144" s="42"/>
-      <c r="K144" s="42"/>
+      <c r="F144" s="51"/>
+      <c r="G144" s="51"/>
+      <c r="H144" s="51"/>
+      <c r="I144" s="54"/>
+      <c r="J144" s="54"/>
+      <c r="K144" s="54"/>
     </row>
     <row r="145" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="39"/>
@@ -3792,329 +3801,321 @@
       <c r="F145" s="39"/>
       <c r="G145" s="39"/>
       <c r="H145" s="39"/>
-      <c r="I145" s="42"/>
-      <c r="J145" s="42"/>
-      <c r="K145" s="42"/>
+      <c r="I145" s="40"/>
+      <c r="J145" s="40"/>
+      <c r="K145" s="40"/>
     </row>
     <row r="146" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" s="43" t="s">
+      <c r="A146" s="39"/>
+      <c r="B146" s="39"/>
+      <c r="C146" s="39"/>
+      <c r="D146" s="39"/>
+      <c r="E146" s="39"/>
+      <c r="F146" s="39"/>
+      <c r="G146" s="39"/>
+      <c r="H146" s="39"/>
+      <c r="I146" s="40"/>
+      <c r="J146" s="40"/>
+      <c r="K146" s="40"/>
+    </row>
+    <row r="147" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B146" s="44"/>
-      <c r="C146" s="45"/>
-      <c r="D146" s="45"/>
-      <c r="E146" s="43"/>
-      <c r="F146" s="43"/>
-      <c r="G146" s="43"/>
-      <c r="H146" s="43"/>
-      <c r="I146" s="46"/>
-      <c r="J146" s="46"/>
-      <c r="K146" s="46"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" s="47"/>
-      <c r="B147" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="C147" s="49"/>
-      <c r="D147" s="49"/>
-      <c r="E147" s="47" t="s">
+      <c r="B147" s="44"/>
+      <c r="C147" s="45"/>
+      <c r="D147" s="45"/>
+      <c r="E147" s="43"/>
+      <c r="F147" s="43"/>
+      <c r="G147" s="43"/>
+      <c r="H147" s="43"/>
+      <c r="I147" s="46"/>
+      <c r="J147" s="46"/>
+      <c r="K147" s="46"/>
+    </row>
+    <row r="148" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" s="47"/>
+      <c r="B148" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="C148" s="49"/>
+      <c r="D148" s="49"/>
+      <c r="E148" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F147" s="47" t="s">
+      <c r="F148" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G147" s="47" t="s">
+      <c r="G148" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="H147" s="47"/>
-      <c r="I147" s="50"/>
-      <c r="J147" s="50"/>
-      <c r="K147" s="50"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" s="39"/>
-      <c r="B148" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="C148" s="41"/>
-      <c r="D148" s="41"/>
-      <c r="E148" s="39"/>
-      <c r="F148" s="39"/>
-      <c r="G148" s="39"/>
-      <c r="H148" s="39"/>
-      <c r="I148" s="42"/>
-      <c r="J148" s="42"/>
-      <c r="K148" s="42"/>
+      <c r="H148" s="47"/>
+      <c r="I148" s="50"/>
+      <c r="J148" s="50"/>
+      <c r="K148" s="50"/>
     </row>
     <row r="149" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="B149" s="44"/>
-      <c r="C149" s="45"/>
-      <c r="D149" s="45"/>
-      <c r="E149" s="43"/>
-      <c r="F149" s="43"/>
-      <c r="G149" s="43"/>
-      <c r="H149" s="43"/>
-      <c r="I149" s="46"/>
-      <c r="J149" s="46"/>
-      <c r="K149" s="46"/>
+      <c r="A149" s="39"/>
+      <c r="B149" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="C149" s="42"/>
+      <c r="D149" s="42"/>
+      <c r="E149" s="39"/>
+      <c r="F149" s="39"/>
+      <c r="G149" s="39"/>
+      <c r="H149" s="39"/>
+      <c r="I149" s="40"/>
+      <c r="J149" s="40"/>
+      <c r="K149" s="40"/>
     </row>
     <row r="150" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150" s="47"/>
-      <c r="B150" s="48"/>
-      <c r="C150" s="49"/>
-      <c r="D150" s="49"/>
-      <c r="E150" s="47" t="s">
+      <c r="A150" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="B150" s="44"/>
+      <c r="C150" s="45"/>
+      <c r="D150" s="45"/>
+      <c r="E150" s="43"/>
+      <c r="F150" s="43"/>
+      <c r="G150" s="43"/>
+      <c r="H150" s="43"/>
+      <c r="I150" s="46"/>
+      <c r="J150" s="46"/>
+      <c r="K150" s="46"/>
+    </row>
+    <row r="151" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" s="47"/>
+      <c r="B151" s="48"/>
+      <c r="C151" s="49"/>
+      <c r="D151" s="49"/>
+      <c r="E151" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F150" s="47" t="s">
+      <c r="F151" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="G150" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H150" s="47"/>
-      <c r="I150" s="50"/>
-      <c r="J150" s="50"/>
-      <c r="K150" s="50"/>
-    </row>
-    <row r="151" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A151" s="39"/>
-      <c r="B151" s="40"/>
-      <c r="C151" s="41"/>
-      <c r="D151" s="41"/>
-      <c r="E151" s="39"/>
-      <c r="F151" s="39"/>
-      <c r="G151" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H151" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="I151" s="42" t="s">
+      <c r="G151" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H151" s="47"/>
+      <c r="I151" s="50"/>
+      <c r="J151" s="50"/>
+      <c r="K151" s="50"/>
+    </row>
+    <row r="152" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" s="39"/>
+      <c r="B152" s="41"/>
+      <c r="C152" s="42"/>
+      <c r="D152" s="42"/>
+      <c r="E152" s="39"/>
+      <c r="F152" s="39"/>
+      <c r="G152" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H152" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="J151" s="42"/>
-      <c r="K151" s="42"/>
-    </row>
-    <row r="152" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A152" s="47"/>
-      <c r="B152" s="48"/>
-      <c r="C152" s="49"/>
-      <c r="D152" s="49"/>
-      <c r="E152" s="47" t="s">
+      <c r="I152" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="J152" s="40"/>
+      <c r="K152" s="40"/>
+    </row>
+    <row r="153" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" s="47"/>
+      <c r="B153" s="48"/>
+      <c r="C153" s="49"/>
+      <c r="D153" s="49"/>
+      <c r="E153" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F152" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="G152" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H152" s="47"/>
-      <c r="I152" s="50"/>
-      <c r="J152" s="50"/>
-      <c r="K152" s="50"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A153" s="39"/>
-      <c r="B153" s="40"/>
-      <c r="C153" s="41"/>
-      <c r="D153" s="41"/>
-      <c r="E153" s="39"/>
-      <c r="F153" s="39"/>
-      <c r="G153" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H153" s="39" t="s">
+      <c r="F153" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="I153" s="42" t="s">
+      <c r="G153" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H153" s="47"/>
+      <c r="I153" s="50"/>
+      <c r="J153" s="50"/>
+      <c r="K153" s="50"/>
+    </row>
+    <row r="154" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" s="39"/>
+      <c r="B154" s="41"/>
+      <c r="C154" s="42"/>
+      <c r="D154" s="42"/>
+      <c r="E154" s="39"/>
+      <c r="F154" s="39"/>
+      <c r="G154" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H154" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="J153" s="42"/>
-      <c r="K153" s="42"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A154" s="47"/>
-      <c r="B154" s="48"/>
-      <c r="C154" s="49"/>
-      <c r="D154" s="49"/>
-      <c r="E154" s="47" t="s">
+      <c r="I154" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="J154" s="40"/>
+      <c r="K154" s="40"/>
+    </row>
+    <row r="155" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" s="47"/>
+      <c r="B155" s="48"/>
+      <c r="C155" s="49"/>
+      <c r="D155" s="49"/>
+      <c r="E155" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F154" s="47" t="s">
+      <c r="F155" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="G154" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H154" s="47"/>
-      <c r="I154" s="50"/>
-      <c r="J154" s="50"/>
-      <c r="K154" s="50"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A155" s="39"/>
-      <c r="B155" s="40"/>
-      <c r="C155" s="41"/>
-      <c r="D155" s="41"/>
-      <c r="E155" s="39"/>
-      <c r="F155" s="39"/>
-      <c r="G155" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H155" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="I155" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="J155" s="42"/>
-      <c r="K155" s="42"/>
+      <c r="G155" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H155" s="47"/>
+      <c r="I155" s="50"/>
+      <c r="J155" s="50"/>
+      <c r="K155" s="50"/>
     </row>
     <row r="156" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="39"/>
-      <c r="B156" s="40"/>
-      <c r="C156" s="41"/>
-      <c r="D156" s="41"/>
+      <c r="B156" s="41"/>
+      <c r="C156" s="42"/>
+      <c r="D156" s="42"/>
       <c r="E156" s="39"/>
       <c r="F156" s="39"/>
       <c r="G156" s="39" t="s">
         <v>20</v>
       </c>
       <c r="H156" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="I156" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="I156" s="42" t="s">
+      <c r="J156" s="40"/>
+      <c r="K156" s="40"/>
+    </row>
+    <row r="157" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" s="39"/>
+      <c r="B157" s="41"/>
+      <c r="C157" s="42"/>
+      <c r="D157" s="42"/>
+      <c r="E157" s="39"/>
+      <c r="F157" s="39"/>
+      <c r="G157" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H157" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="J156" s="42"/>
-      <c r="K156" s="42"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A157" s="47"/>
-      <c r="B157" s="48"/>
-      <c r="C157" s="49"/>
-      <c r="D157" s="49"/>
-      <c r="E157" s="47" t="s">
+      <c r="I157" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="J157" s="40"/>
+      <c r="K157" s="40"/>
+    </row>
+    <row r="158" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" s="47"/>
+      <c r="B158" s="48"/>
+      <c r="C158" s="49"/>
+      <c r="D158" s="49"/>
+      <c r="E158" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F157" s="47" t="s">
+      <c r="F158" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="G157" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H157" s="47"/>
-      <c r="I157" s="50"/>
-      <c r="J157" s="50"/>
-      <c r="K157" s="50"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158" s="39"/>
-      <c r="B158" s="40"/>
-      <c r="C158" s="41"/>
-      <c r="D158" s="41"/>
-      <c r="E158" s="39"/>
-      <c r="F158" s="39"/>
-      <c r="G158" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H158" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="I158" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="J158" s="42"/>
-      <c r="K158" s="42"/>
+      <c r="G158" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H158" s="47"/>
+      <c r="I158" s="50"/>
+      <c r="J158" s="50"/>
+      <c r="K158" s="50"/>
     </row>
     <row r="159" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="39"/>
-      <c r="B159" s="40"/>
-      <c r="C159" s="41"/>
-      <c r="D159" s="41"/>
+      <c r="B159" s="41"/>
+      <c r="C159" s="42"/>
+      <c r="D159" s="42"/>
       <c r="E159" s="39"/>
       <c r="F159" s="39"/>
       <c r="G159" s="39" t="s">
         <v>20</v>
       </c>
       <c r="H159" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="I159" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="I159" s="42" t="s">
+      <c r="J159" s="40"/>
+      <c r="K159" s="40"/>
+    </row>
+    <row r="160" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" s="39"/>
+      <c r="B160" s="41"/>
+      <c r="C160" s="42"/>
+      <c r="D160" s="42"/>
+      <c r="E160" s="39"/>
+      <c r="F160" s="39"/>
+      <c r="G160" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H160" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="J159" s="42"/>
-      <c r="K159" s="42"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A160" s="47"/>
-      <c r="B160" s="48"/>
-      <c r="C160" s="49"/>
-      <c r="D160" s="49"/>
-      <c r="E160" s="47" t="s">
+      <c r="I160" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="J160" s="40"/>
+      <c r="K160" s="40"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" s="47"/>
+      <c r="B161" s="48"/>
+      <c r="C161" s="49"/>
+      <c r="D161" s="49"/>
+      <c r="E161" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F160" s="47" t="s">
+      <c r="F161" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="G160" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H160" s="47"/>
-      <c r="I160" s="50"/>
-      <c r="J160" s="50"/>
-      <c r="K160" s="50"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A161" s="39"/>
-      <c r="B161" s="40"/>
-      <c r="C161" s="41"/>
-      <c r="D161" s="41"/>
-      <c r="E161" s="39"/>
-      <c r="F161" s="39"/>
-      <c r="G161" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H161" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="I161" s="42" t="s">
+      <c r="G161" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H161" s="47"/>
+      <c r="I161" s="50"/>
+      <c r="J161" s="50"/>
+      <c r="K161" s="50"/>
+    </row>
+    <row r="162" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" s="39"/>
+      <c r="B162" s="41"/>
+      <c r="C162" s="42"/>
+      <c r="D162" s="42"/>
+      <c r="E162" s="39"/>
+      <c r="F162" s="39"/>
+      <c r="G162" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H162" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="J161" s="42"/>
-      <c r="K161" s="42"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A162" s="55"/>
-      <c r="B162" s="56" t="s">
+      <c r="I162" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C162" s="57"/>
-      <c r="D162" s="57"/>
-      <c r="E162" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="F162" s="55"/>
-      <c r="G162" s="55"/>
-      <c r="H162" s="55" t="s">
-        <v>170</v>
-      </c>
-      <c r="I162" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="J162" s="58"/>
-      <c r="K162" s="58"/>
+      <c r="J162" s="40"/>
+      <c r="K162" s="40"/>
     </row>
     <row r="163" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="55"/>
       <c r="B163" s="56" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C163" s="57"/>
       <c r="D163" s="57"/>
@@ -4124,84 +4125,92 @@
       <c r="F163" s="55"/>
       <c r="G163" s="55"/>
       <c r="H163" s="55" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I163" s="58" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J163" s="58"/>
       <c r="K163" s="58"/>
     </row>
     <row r="164" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A164" s="59"/>
-      <c r="B164" s="60"/>
-      <c r="C164" s="61"/>
-      <c r="D164" s="61"/>
-      <c r="E164" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="F164" s="59"/>
-      <c r="G164" s="59"/>
-      <c r="H164" s="59"/>
-      <c r="I164" s="62"/>
-      <c r="J164" s="62"/>
-      <c r="K164" s="62"/>
+      <c r="A164" s="55"/>
+      <c r="B164" s="56" t="s">
+        <v>173</v>
+      </c>
+      <c r="C164" s="57"/>
+      <c r="D164" s="57"/>
+      <c r="E164" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="F164" s="55"/>
+      <c r="G164" s="55"/>
+      <c r="H164" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="I164" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="J164" s="58"/>
+      <c r="K164" s="58"/>
     </row>
     <row r="165" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A165" s="39"/>
-      <c r="B165" s="39"/>
-      <c r="C165" s="39"/>
-      <c r="D165" s="39"/>
-      <c r="E165" s="39"/>
-      <c r="F165" s="39"/>
-      <c r="G165" s="39"/>
-      <c r="H165" s="39"/>
-      <c r="I165" s="42"/>
-      <c r="J165" s="42"/>
-      <c r="K165" s="42"/>
+      <c r="A165" s="59"/>
+      <c r="B165" s="60"/>
+      <c r="C165" s="61"/>
+      <c r="D165" s="61"/>
+      <c r="E165" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="F165" s="59"/>
+      <c r="G165" s="59"/>
+      <c r="H165" s="59"/>
+      <c r="I165" s="62"/>
+      <c r="J165" s="62"/>
+      <c r="K165" s="62"/>
     </row>
     <row r="166" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A166" s="51"/>
-      <c r="B166" s="52"/>
-      <c r="C166" s="53"/>
-      <c r="D166" s="53"/>
-      <c r="E166" s="51" t="s">
+      <c r="A166" s="39"/>
+      <c r="B166" s="39"/>
+      <c r="C166" s="39"/>
+      <c r="D166" s="39"/>
+      <c r="E166" s="39"/>
+      <c r="F166" s="39"/>
+      <c r="G166" s="39"/>
+      <c r="H166" s="39"/>
+      <c r="I166" s="40"/>
+      <c r="J166" s="40"/>
+      <c r="K166" s="40"/>
+    </row>
+    <row r="167" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" s="51"/>
+      <c r="B167" s="52"/>
+      <c r="C167" s="53"/>
+      <c r="D167" s="53"/>
+      <c r="E167" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F166" s="51"/>
-      <c r="G166" s="51"/>
-      <c r="H166" s="51"/>
-      <c r="I166" s="54"/>
-      <c r="J166" s="54"/>
-      <c r="K166" s="54"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="B167" s="44"/>
-      <c r="C167" s="45"/>
-      <c r="D167" s="45"/>
-      <c r="E167" s="43"/>
-      <c r="F167" s="43"/>
-      <c r="G167" s="43"/>
-      <c r="H167" s="43"/>
-      <c r="I167" s="46"/>
-      <c r="J167" s="46"/>
-      <c r="K167" s="46"/>
+      <c r="F167" s="51"/>
+      <c r="G167" s="51"/>
+      <c r="H167" s="51"/>
+      <c r="I167" s="54"/>
+      <c r="J167" s="54"/>
+      <c r="K167" s="54"/>
     </row>
     <row r="168" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A168" s="39"/>
-      <c r="B168" s="39"/>
-      <c r="C168" s="39"/>
-      <c r="D168" s="39"/>
-      <c r="E168" s="39"/>
-      <c r="F168" s="39"/>
-      <c r="G168" s="39"/>
-      <c r="H168" s="39"/>
-      <c r="I168" s="42"/>
-      <c r="J168" s="42"/>
-      <c r="K168" s="42"/>
+      <c r="A168" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="B168" s="44"/>
+      <c r="C168" s="45"/>
+      <c r="D168" s="45"/>
+      <c r="E168" s="43"/>
+      <c r="F168" s="43"/>
+      <c r="G168" s="43"/>
+      <c r="H168" s="43"/>
+      <c r="I168" s="46"/>
+      <c r="J168" s="46"/>
+      <c r="K168" s="46"/>
     </row>
     <row r="169" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="39"/>
@@ -4212,107 +4221,99 @@
       <c r="F169" s="39"/>
       <c r="G169" s="39"/>
       <c r="H169" s="39"/>
-      <c r="I169" s="42"/>
-      <c r="J169" s="42"/>
-      <c r="K169" s="42"/>
+      <c r="I169" s="40"/>
+      <c r="J169" s="40"/>
+      <c r="K169" s="40"/>
     </row>
     <row r="170" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A170" s="47"/>
-      <c r="B170" s="48"/>
-      <c r="C170" s="49"/>
-      <c r="D170" s="49"/>
-      <c r="E170" s="47" t="s">
+      <c r="A170" s="39"/>
+      <c r="B170" s="39"/>
+      <c r="C170" s="39"/>
+      <c r="D170" s="39"/>
+      <c r="E170" s="39"/>
+      <c r="F170" s="39"/>
+      <c r="G170" s="39"/>
+      <c r="H170" s="39"/>
+      <c r="I170" s="40"/>
+      <c r="J170" s="40"/>
+      <c r="K170" s="40"/>
+    </row>
+    <row r="171" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" s="47"/>
+      <c r="B171" s="48"/>
+      <c r="C171" s="49"/>
+      <c r="D171" s="49"/>
+      <c r="E171" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F170" s="47" t="s">
+      <c r="F171" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="G170" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H170" s="47"/>
-      <c r="I170" s="50"/>
-      <c r="J170" s="50"/>
-      <c r="K170" s="50"/>
-    </row>
-    <row r="171" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A171" s="39"/>
-      <c r="B171" s="40"/>
-      <c r="C171" s="41"/>
-      <c r="D171" s="41"/>
-      <c r="E171" s="39"/>
-      <c r="F171" s="39"/>
-      <c r="G171" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H171" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="I171" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="J171" s="42"/>
-      <c r="K171" s="42"/>
+      <c r="G171" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H171" s="47"/>
+      <c r="I171" s="50"/>
+      <c r="J171" s="50"/>
+      <c r="K171" s="50"/>
     </row>
     <row r="172" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="39"/>
-      <c r="B172" s="40"/>
-      <c r="C172" s="41"/>
-      <c r="D172" s="41"/>
+      <c r="B172" s="41"/>
+      <c r="C172" s="42"/>
+      <c r="D172" s="42"/>
       <c r="E172" s="39"/>
       <c r="F172" s="39"/>
       <c r="G172" s="39" t="s">
         <v>20</v>
       </c>
       <c r="H172" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="I172" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="I172" s="42" t="s">
+      <c r="J172" s="40"/>
+      <c r="K172" s="40"/>
+    </row>
+    <row r="173" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" s="39"/>
+      <c r="B173" s="41"/>
+      <c r="C173" s="42"/>
+      <c r="D173" s="42"/>
+      <c r="E173" s="39"/>
+      <c r="F173" s="39"/>
+      <c r="G173" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H173" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="J172" s="42"/>
-      <c r="K172" s="42"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A173" s="51"/>
-      <c r="B173" s="52"/>
-      <c r="C173" s="53"/>
-      <c r="D173" s="53"/>
-      <c r="E173" s="51" t="s">
+      <c r="I173" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="J173" s="40"/>
+      <c r="K173" s="40"/>
+    </row>
+    <row r="174" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" s="51"/>
+      <c r="B174" s="52"/>
+      <c r="C174" s="53"/>
+      <c r="D174" s="53"/>
+      <c r="E174" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F173" s="51"/>
-      <c r="G173" s="51"/>
-      <c r="H173" s="51"/>
-      <c r="I173" s="54"/>
-      <c r="J173" s="54"/>
-      <c r="K173" s="54"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A174" s="55"/>
-      <c r="B174" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="C174" s="57"/>
-      <c r="D174" s="57"/>
-      <c r="E174" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="F174" s="55"/>
-      <c r="G174" s="55"/>
-      <c r="H174" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="I174" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="J174" s="58"/>
-      <c r="K174" s="58"/>
+      <c r="F174" s="51"/>
+      <c r="G174" s="51"/>
+      <c r="H174" s="51"/>
+      <c r="I174" s="54"/>
+      <c r="J174" s="54"/>
+      <c r="K174" s="54"/>
     </row>
     <row r="175" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="55"/>
       <c r="B175" s="56" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C175" s="57"/>
       <c r="D175" s="57"/>
@@ -4322,102 +4323,104 @@
       <c r="F175" s="55"/>
       <c r="G175" s="55"/>
       <c r="H175" s="55" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I175" s="58" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J175" s="58"/>
       <c r="K175" s="58"/>
     </row>
     <row r="176" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A176" s="59"/>
-      <c r="B176" s="60" t="s">
+      <c r="A176" s="55"/>
+      <c r="B176" s="56" t="s">
+        <v>182</v>
+      </c>
+      <c r="C176" s="57"/>
+      <c r="D176" s="57"/>
+      <c r="E176" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="F176" s="55"/>
+      <c r="G176" s="55"/>
+      <c r="H176" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="I176" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="J176" s="58"/>
+      <c r="K176" s="58"/>
+    </row>
+    <row r="177" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" s="59"/>
+      <c r="B177" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="C176" s="61"/>
-      <c r="D176" s="61"/>
-      <c r="E176" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="F176" s="59"/>
-      <c r="G176" s="59"/>
-      <c r="H176" s="59"/>
-      <c r="I176" s="62"/>
-      <c r="J176" s="62"/>
-      <c r="K176" s="62"/>
-    </row>
-    <row r="177" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A177" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="B177" s="44"/>
-      <c r="C177" s="45"/>
-      <c r="D177" s="45"/>
-      <c r="E177" s="43"/>
-      <c r="F177" s="43"/>
-      <c r="G177" s="43"/>
-      <c r="H177" s="43"/>
-      <c r="I177" s="46"/>
-      <c r="J177" s="46"/>
-      <c r="K177" s="46"/>
+      <c r="C177" s="61"/>
+      <c r="D177" s="61"/>
+      <c r="E177" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="F177" s="59"/>
+      <c r="G177" s="59"/>
+      <c r="H177" s="59"/>
+      <c r="I177" s="62"/>
+      <c r="J177" s="62"/>
+      <c r="K177" s="62"/>
     </row>
     <row r="178" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A178" s="47"/>
-      <c r="B178" s="48"/>
-      <c r="C178" s="49"/>
-      <c r="D178" s="49"/>
-      <c r="E178" s="47" t="s">
+      <c r="A178" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="B178" s="44"/>
+      <c r="C178" s="45"/>
+      <c r="D178" s="45"/>
+      <c r="E178" s="43"/>
+      <c r="F178" s="43"/>
+      <c r="G178" s="43"/>
+      <c r="H178" s="43"/>
+      <c r="I178" s="46"/>
+      <c r="J178" s="46"/>
+      <c r="K178" s="46"/>
+    </row>
+    <row r="179" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" s="47"/>
+      <c r="B179" s="48"/>
+      <c r="C179" s="49"/>
+      <c r="D179" s="49"/>
+      <c r="E179" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F178" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="G178" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H178" s="47"/>
-      <c r="I178" s="50"/>
-      <c r="J178" s="50"/>
-      <c r="K178" s="50"/>
-    </row>
-    <row r="179" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179" s="39"/>
-      <c r="B179" s="40"/>
-      <c r="C179" s="41"/>
-      <c r="D179" s="41"/>
-      <c r="E179" s="39"/>
-      <c r="F179" s="39"/>
-      <c r="G179" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H179" s="39" t="s">
+      <c r="F179" s="47" t="s">
         <v>185</v>
       </c>
-      <c r="I179" s="42" t="s">
+      <c r="G179" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H179" s="47"/>
+      <c r="I179" s="50"/>
+      <c r="J179" s="50"/>
+      <c r="K179" s="50"/>
+    </row>
+    <row r="180" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" s="39"/>
+      <c r="B180" s="41"/>
+      <c r="C180" s="42"/>
+      <c r="D180" s="42"/>
+      <c r="E180" s="39"/>
+      <c r="F180" s="39"/>
+      <c r="G180" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H180" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="J179" s="42"/>
-      <c r="K179" s="42"/>
-    </row>
-    <row r="180" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A180" s="47"/>
-      <c r="B180" s="48"/>
-      <c r="C180" s="49"/>
-      <c r="D180" s="49"/>
-      <c r="E180" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F180" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="G180" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H180" s="47"/>
-      <c r="I180" s="50"/>
-      <c r="J180" s="50"/>
-      <c r="K180" s="50"/>
+      <c r="I180" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="J180" s="40"/>
+      <c r="K180" s="40"/>
     </row>
     <row r="181" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="47"/>
@@ -4428,7 +4431,7 @@
         <v>15</v>
       </c>
       <c r="F181" s="47" t="s">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="G181" s="47" t="s">
         <v>20</v>
@@ -4450,7 +4453,7 @@
         <v>145</v>
       </c>
       <c r="G182" s="47" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H182" s="47"/>
       <c r="I182" s="50"/>
@@ -4458,345 +4461,343 @@
       <c r="K182" s="50"/>
     </row>
     <row r="183" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A183" s="39"/>
-      <c r="B183" s="40"/>
-      <c r="C183" s="41"/>
-      <c r="D183" s="41"/>
-      <c r="E183" s="39"/>
-      <c r="F183" s="39"/>
-      <c r="G183" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H183" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="I183" s="42" t="s">
+      <c r="A183" s="47"/>
+      <c r="B183" s="48"/>
+      <c r="C183" s="49"/>
+      <c r="D183" s="49"/>
+      <c r="E183" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F183" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="G183" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="H183" s="47"/>
+      <c r="I183" s="50"/>
+      <c r="J183" s="50"/>
+      <c r="K183" s="50"/>
+    </row>
+    <row r="184" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" s="39"/>
+      <c r="B184" s="41"/>
+      <c r="C184" s="42"/>
+      <c r="D184" s="42"/>
+      <c r="E184" s="39"/>
+      <c r="F184" s="39"/>
+      <c r="G184" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H184" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="J183" s="42"/>
-      <c r="K183" s="42"/>
-    </row>
-    <row r="184" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184" s="51"/>
-      <c r="B184" s="52"/>
-      <c r="C184" s="53"/>
-      <c r="D184" s="53"/>
-      <c r="E184" s="51" t="s">
+      <c r="I184" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="J184" s="40"/>
+      <c r="K184" s="40"/>
+    </row>
+    <row r="185" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" s="51"/>
+      <c r="B185" s="52"/>
+      <c r="C185" s="53"/>
+      <c r="D185" s="53"/>
+      <c r="E185" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F184" s="51"/>
-      <c r="G184" s="51"/>
-      <c r="H184" s="51"/>
-      <c r="I184" s="54"/>
-      <c r="J184" s="54"/>
-      <c r="K184" s="54"/>
-    </row>
-    <row r="185" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A185" s="43" t="s">
-        <v>172</v>
-      </c>
-      <c r="B185" s="44"/>
-      <c r="C185" s="45"/>
-      <c r="D185" s="45"/>
-      <c r="E185" s="43"/>
-      <c r="F185" s="43"/>
-      <c r="G185" s="43"/>
-      <c r="H185" s="43"/>
-      <c r="I185" s="46"/>
-      <c r="J185" s="46"/>
-      <c r="K185" s="46"/>
+      <c r="F185" s="51"/>
+      <c r="G185" s="51"/>
+      <c r="H185" s="51"/>
+      <c r="I185" s="54"/>
+      <c r="J185" s="54"/>
+      <c r="K185" s="54"/>
     </row>
     <row r="186" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A186" s="47"/>
-      <c r="B186" s="48"/>
-      <c r="C186" s="49"/>
-      <c r="D186" s="49"/>
-      <c r="E186" s="47" t="s">
+      <c r="A186" s="43" t="s">
+        <v>173</v>
+      </c>
+      <c r="B186" s="44"/>
+      <c r="C186" s="45"/>
+      <c r="D186" s="45"/>
+      <c r="E186" s="43"/>
+      <c r="F186" s="43"/>
+      <c r="G186" s="43"/>
+      <c r="H186" s="43"/>
+      <c r="I186" s="46"/>
+      <c r="J186" s="46"/>
+      <c r="K186" s="46"/>
+    </row>
+    <row r="187" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" s="47"/>
+      <c r="B187" s="48"/>
+      <c r="C187" s="49"/>
+      <c r="D187" s="49"/>
+      <c r="E187" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F186" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="G186" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H186" s="47"/>
-      <c r="I186" s="50"/>
-      <c r="J186" s="50"/>
-      <c r="K186" s="50"/>
-    </row>
-    <row r="187" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187" s="39"/>
-      <c r="B187" s="40"/>
-      <c r="C187" s="41"/>
-      <c r="D187" s="41"/>
-      <c r="E187" s="39"/>
-      <c r="F187" s="39"/>
-      <c r="G187" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H187" s="39" t="s">
-        <v>189</v>
-      </c>
-      <c r="I187" s="42" t="s">
+      <c r="F187" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G187" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H187" s="47"/>
+      <c r="I187" s="50"/>
+      <c r="J187" s="50"/>
+      <c r="K187" s="50"/>
+    </row>
+    <row r="188" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" s="39"/>
+      <c r="B188" s="41"/>
+      <c r="C188" s="42"/>
+      <c r="D188" s="42"/>
+      <c r="E188" s="39"/>
+      <c r="F188" s="39"/>
+      <c r="G188" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H188" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="J187" s="42"/>
-      <c r="K187" s="42"/>
-    </row>
-    <row r="188" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188" s="47"/>
-      <c r="B188" s="48"/>
-      <c r="C188" s="49"/>
-      <c r="D188" s="49"/>
-      <c r="E188" s="47" t="s">
+      <c r="I188" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="J188" s="40"/>
+      <c r="K188" s="40"/>
+    </row>
+    <row r="189" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" s="47"/>
+      <c r="B189" s="48"/>
+      <c r="C189" s="49"/>
+      <c r="D189" s="49"/>
+      <c r="E189" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F188" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="G188" s="47" t="s">
+      <c r="F189" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="G189" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="H188" s="47"/>
-      <c r="I188" s="50"/>
-      <c r="J188" s="50"/>
-      <c r="K188" s="50"/>
-    </row>
-    <row r="189" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189" s="39"/>
-      <c r="B189" s="39"/>
-      <c r="C189" s="39"/>
-      <c r="D189" s="39"/>
-      <c r="E189" s="39"/>
-      <c r="F189" s="39"/>
-      <c r="G189" s="39"/>
-      <c r="H189" s="39"/>
-      <c r="I189" s="42"/>
-      <c r="J189" s="42"/>
-      <c r="K189" s="42"/>
+      <c r="H189" s="47"/>
+      <c r="I189" s="50"/>
+      <c r="J189" s="50"/>
+      <c r="K189" s="50"/>
     </row>
     <row r="190" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190" s="51"/>
-      <c r="B190" s="52"/>
-      <c r="C190" s="53"/>
-      <c r="D190" s="53"/>
-      <c r="E190" s="51" t="s">
+      <c r="A190" s="39"/>
+      <c r="B190" s="39"/>
+      <c r="C190" s="39"/>
+      <c r="D190" s="39"/>
+      <c r="E190" s="39"/>
+      <c r="F190" s="39"/>
+      <c r="G190" s="39"/>
+      <c r="H190" s="39"/>
+      <c r="I190" s="40"/>
+      <c r="J190" s="40"/>
+      <c r="K190" s="40"/>
+    </row>
+    <row r="191" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" s="51"/>
+      <c r="B191" s="52"/>
+      <c r="C191" s="53"/>
+      <c r="D191" s="53"/>
+      <c r="E191" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F190" s="51"/>
-      <c r="G190" s="51"/>
-      <c r="H190" s="51"/>
-      <c r="I190" s="54"/>
-      <c r="J190" s="54"/>
-      <c r="K190" s="54"/>
-    </row>
-    <row r="191" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A191" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="B191" s="44"/>
-      <c r="C191" s="45"/>
-      <c r="D191" s="45"/>
-      <c r="E191" s="43"/>
-      <c r="F191" s="43"/>
-      <c r="G191" s="43"/>
-      <c r="H191" s="43"/>
-      <c r="I191" s="46"/>
-      <c r="J191" s="46"/>
-      <c r="K191" s="46"/>
+      <c r="F191" s="51"/>
+      <c r="G191" s="51"/>
+      <c r="H191" s="51"/>
+      <c r="I191" s="54"/>
+      <c r="J191" s="54"/>
+      <c r="K191" s="54"/>
     </row>
     <row r="192" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A192" s="47"/>
-      <c r="B192" s="48"/>
-      <c r="C192" s="49"/>
-      <c r="D192" s="49"/>
-      <c r="E192" s="47" t="s">
+      <c r="A192" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="B192" s="44"/>
+      <c r="C192" s="45"/>
+      <c r="D192" s="45"/>
+      <c r="E192" s="43"/>
+      <c r="F192" s="43"/>
+      <c r="G192" s="43"/>
+      <c r="H192" s="43"/>
+      <c r="I192" s="46"/>
+      <c r="J192" s="46"/>
+      <c r="K192" s="46"/>
+    </row>
+    <row r="193" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" s="47"/>
+      <c r="B193" s="48"/>
+      <c r="C193" s="49"/>
+      <c r="D193" s="49"/>
+      <c r="E193" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F192" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="G192" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H192" s="47"/>
-      <c r="I192" s="50"/>
-      <c r="J192" s="50"/>
-      <c r="K192" s="50"/>
-    </row>
-    <row r="193" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A193" s="39"/>
-      <c r="B193" s="40"/>
-      <c r="C193" s="41"/>
-      <c r="D193" s="41"/>
-      <c r="E193" s="39"/>
-      <c r="F193" s="39"/>
-      <c r="G193" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H193" s="39" t="s">
-        <v>191</v>
-      </c>
-      <c r="I193" s="42" t="s">
+      <c r="F193" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G193" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H193" s="47"/>
+      <c r="I193" s="50"/>
+      <c r="J193" s="50"/>
+      <c r="K193" s="50"/>
+    </row>
+    <row r="194" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" s="39"/>
+      <c r="B194" s="41"/>
+      <c r="C194" s="42"/>
+      <c r="D194" s="42"/>
+      <c r="E194" s="39"/>
+      <c r="F194" s="39"/>
+      <c r="G194" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H194" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="J193" s="42"/>
-      <c r="K193" s="42"/>
-    </row>
-    <row r="194" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A194" s="47"/>
-      <c r="B194" s="48"/>
-      <c r="C194" s="49"/>
-      <c r="D194" s="49"/>
-      <c r="E194" s="47" t="s">
+      <c r="I194" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="J194" s="40"/>
+      <c r="K194" s="40"/>
+    </row>
+    <row r="195" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" s="47"/>
+      <c r="B195" s="48"/>
+      <c r="C195" s="49"/>
+      <c r="D195" s="49"/>
+      <c r="E195" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F194" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="G194" s="47" t="s">
+      <c r="F195" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="G195" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="H194" s="47"/>
-      <c r="I194" s="50"/>
-      <c r="J194" s="50"/>
-      <c r="K194" s="50"/>
-    </row>
-    <row r="195" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A195" s="39"/>
-      <c r="B195" s="39"/>
-      <c r="C195" s="39"/>
-      <c r="D195" s="39"/>
-      <c r="E195" s="39"/>
-      <c r="F195" s="39"/>
-      <c r="G195" s="39"/>
-      <c r="H195" s="39"/>
-      <c r="I195" s="42"/>
-      <c r="J195" s="42"/>
-      <c r="K195" s="42"/>
+      <c r="H195" s="47"/>
+      <c r="I195" s="50"/>
+      <c r="J195" s="50"/>
+      <c r="K195" s="50"/>
     </row>
     <row r="196" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A196" s="51"/>
-      <c r="B196" s="52"/>
-      <c r="C196" s="53"/>
-      <c r="D196" s="53"/>
-      <c r="E196" s="51" t="s">
+      <c r="A196" s="39"/>
+      <c r="B196" s="39"/>
+      <c r="C196" s="39"/>
+      <c r="D196" s="39"/>
+      <c r="E196" s="39"/>
+      <c r="F196" s="39"/>
+      <c r="G196" s="39"/>
+      <c r="H196" s="39"/>
+      <c r="I196" s="40"/>
+      <c r="J196" s="40"/>
+      <c r="K196" s="40"/>
+    </row>
+    <row r="197" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" s="51"/>
+      <c r="B197" s="52"/>
+      <c r="C197" s="53"/>
+      <c r="D197" s="53"/>
+      <c r="E197" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F196" s="51"/>
-      <c r="G196" s="51"/>
-      <c r="H196" s="51"/>
-      <c r="I196" s="54"/>
-      <c r="J196" s="54"/>
-      <c r="K196" s="54"/>
-    </row>
-    <row r="197" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A197" s="43" t="s">
+      <c r="F197" s="51"/>
+      <c r="G197" s="51"/>
+      <c r="H197" s="51"/>
+      <c r="I197" s="54"/>
+      <c r="J197" s="54"/>
+      <c r="K197" s="54"/>
+    </row>
+    <row r="198" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="B197" s="44"/>
-      <c r="C197" s="45"/>
-      <c r="D197" s="45"/>
-      <c r="E197" s="43"/>
-      <c r="F197" s="43"/>
-      <c r="G197" s="43"/>
-      <c r="H197" s="43"/>
-      <c r="I197" s="46"/>
-      <c r="J197" s="46"/>
-      <c r="K197" s="46"/>
-    </row>
-    <row r="198" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A198" s="47"/>
-      <c r="B198" s="48"/>
-      <c r="C198" s="49"/>
-      <c r="D198" s="49"/>
-      <c r="E198" s="47" t="s">
+      <c r="B198" s="44"/>
+      <c r="C198" s="45"/>
+      <c r="D198" s="45"/>
+      <c r="E198" s="43"/>
+      <c r="F198" s="43"/>
+      <c r="G198" s="43"/>
+      <c r="H198" s="43"/>
+      <c r="I198" s="46"/>
+      <c r="J198" s="46"/>
+      <c r="K198" s="46"/>
+    </row>
+    <row r="199" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" s="47"/>
+      <c r="B199" s="48"/>
+      <c r="C199" s="49"/>
+      <c r="D199" s="49"/>
+      <c r="E199" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F198" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="G198" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H198" s="47"/>
-      <c r="I198" s="50"/>
-      <c r="J198" s="50"/>
-      <c r="K198" s="50"/>
-    </row>
-    <row r="199" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A199" s="39"/>
-      <c r="B199" s="40"/>
-      <c r="C199" s="41"/>
-      <c r="D199" s="41"/>
-      <c r="E199" s="39"/>
-      <c r="F199" s="39"/>
-      <c r="G199" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H199" s="39" t="s">
+      <c r="F199" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="I199" s="42" t="s">
-        <v>195</v>
-      </c>
-      <c r="J199" s="42"/>
-      <c r="K199" s="42"/>
+      <c r="G199" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H199" s="47"/>
+      <c r="I199" s="50"/>
+      <c r="J199" s="50"/>
+      <c r="K199" s="50"/>
     </row>
     <row r="200" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="39"/>
-      <c r="B200" s="39"/>
-      <c r="C200" s="39"/>
-      <c r="D200" s="39"/>
+      <c r="B200" s="41"/>
+      <c r="C200" s="42"/>
+      <c r="D200" s="42"/>
       <c r="E200" s="39"/>
       <c r="F200" s="39"/>
-      <c r="G200" s="39"/>
-      <c r="H200" s="39"/>
-      <c r="I200" s="42"/>
-      <c r="J200" s="42"/>
-      <c r="K200" s="42"/>
+      <c r="G200" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H200" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="I200" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="J200" s="40"/>
+      <c r="K200" s="40"/>
     </row>
     <row r="201" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A201" s="51"/>
-      <c r="B201" s="52"/>
-      <c r="C201" s="53"/>
-      <c r="D201" s="53"/>
-      <c r="E201" s="51" t="s">
+      <c r="A201" s="39"/>
+      <c r="B201" s="39"/>
+      <c r="C201" s="39"/>
+      <c r="D201" s="39"/>
+      <c r="E201" s="39"/>
+      <c r="F201" s="39"/>
+      <c r="G201" s="39"/>
+      <c r="H201" s="39"/>
+      <c r="I201" s="40"/>
+      <c r="J201" s="40"/>
+      <c r="K201" s="40"/>
+    </row>
+    <row r="202" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A202" s="51"/>
+      <c r="B202" s="52"/>
+      <c r="C202" s="53"/>
+      <c r="D202" s="53"/>
+      <c r="E202" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F201" s="51"/>
-      <c r="G201" s="51"/>
-      <c r="H201" s="51"/>
-      <c r="I201" s="54"/>
-      <c r="J201" s="54"/>
-      <c r="K201" s="54"/>
-    </row>
-    <row r="202" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A202" s="55"/>
-      <c r="B202" s="56" t="s">
-        <v>196</v>
-      </c>
-      <c r="C202" s="57"/>
-      <c r="D202" s="57"/>
-      <c r="E202" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="F202" s="55"/>
-      <c r="G202" s="55"/>
-      <c r="H202" s="55" t="s">
-        <v>197</v>
-      </c>
-      <c r="I202" s="58" t="s">
-        <v>198</v>
-      </c>
-      <c r="J202" s="58"/>
-      <c r="K202" s="58"/>
+      <c r="F202" s="51"/>
+      <c r="G202" s="51"/>
+      <c r="H202" s="51"/>
+      <c r="I202" s="54"/>
+      <c r="J202" s="54"/>
+      <c r="K202" s="54"/>
     </row>
     <row r="203" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="55"/>
       <c r="B203" s="56" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C203" s="57"/>
       <c r="D203" s="57"/>
@@ -4806,64 +4807,66 @@
       <c r="F203" s="55"/>
       <c r="G203" s="55"/>
       <c r="H203" s="55" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I203" s="58" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J203" s="58"/>
       <c r="K203" s="58"/>
     </row>
     <row r="204" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A204" s="59"/>
-      <c r="B204" s="60" t="s">
+      <c r="A204" s="55"/>
+      <c r="B204" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="C204" s="57"/>
+      <c r="D204" s="57"/>
+      <c r="E204" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="F204" s="55"/>
+      <c r="G204" s="55"/>
+      <c r="H204" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="I204" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="J204" s="58"/>
+      <c r="K204" s="58"/>
+    </row>
+    <row r="205" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A205" s="59"/>
+      <c r="B205" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="C204" s="61"/>
-      <c r="D204" s="61"/>
-      <c r="E204" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="F204" s="59"/>
-      <c r="G204" s="59"/>
-      <c r="H204" s="59"/>
-      <c r="I204" s="62"/>
-      <c r="J204" s="62"/>
-      <c r="K204" s="62"/>
-    </row>
-    <row r="205" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A205" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="B205" s="44"/>
-      <c r="C205" s="45"/>
-      <c r="D205" s="45"/>
-      <c r="E205" s="43"/>
-      <c r="F205" s="43"/>
-      <c r="G205" s="43"/>
-      <c r="H205" s="43"/>
-      <c r="I205" s="46"/>
-      <c r="J205" s="46"/>
-      <c r="K205" s="46"/>
+      <c r="C205" s="61"/>
+      <c r="D205" s="61"/>
+      <c r="E205" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="F205" s="59"/>
+      <c r="G205" s="59"/>
+      <c r="H205" s="59"/>
+      <c r="I205" s="62"/>
+      <c r="J205" s="62"/>
+      <c r="K205" s="62"/>
     </row>
     <row r="206" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A206" s="47"/>
-      <c r="B206" s="48"/>
-      <c r="C206" s="49"/>
-      <c r="D206" s="49"/>
-      <c r="E206" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F206" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="G206" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H206" s="47"/>
-      <c r="I206" s="50"/>
-      <c r="J206" s="50"/>
-      <c r="K206" s="50"/>
+      <c r="A206" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="B206" s="44"/>
+      <c r="C206" s="45"/>
+      <c r="D206" s="45"/>
+      <c r="E206" s="43"/>
+      <c r="F206" s="43"/>
+      <c r="G206" s="43"/>
+      <c r="H206" s="43"/>
+      <c r="I206" s="46"/>
+      <c r="J206" s="46"/>
+      <c r="K206" s="46"/>
     </row>
     <row r="207" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="47"/>
@@ -4874,7 +4877,7 @@
         <v>15</v>
       </c>
       <c r="F207" s="47" t="s">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="G207" s="47" t="s">
         <v>20</v>
@@ -4885,236 +4888,254 @@
       <c r="K207" s="50"/>
     </row>
     <row r="208" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A208" s="39"/>
-      <c r="B208" s="40"/>
-      <c r="C208" s="41"/>
-      <c r="D208" s="41"/>
-      <c r="E208" s="39"/>
-      <c r="F208" s="39"/>
-      <c r="G208" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H208" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="I208" s="42" t="s">
-        <v>203</v>
-      </c>
-      <c r="J208" s="42"/>
-      <c r="K208" s="42"/>
+      <c r="A208" s="47"/>
+      <c r="B208" s="48"/>
+      <c r="C208" s="49"/>
+      <c r="D208" s="49"/>
+      <c r="E208" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F208" s="47" t="s">
+        <v>145</v>
+      </c>
+      <c r="G208" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H208" s="47"/>
+      <c r="I208" s="50"/>
+      <c r="J208" s="50"/>
+      <c r="K208" s="50"/>
     </row>
     <row r="209" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="39"/>
-      <c r="B209" s="39"/>
-      <c r="C209" s="39"/>
-      <c r="D209" s="39"/>
+      <c r="B209" s="41"/>
+      <c r="C209" s="42"/>
+      <c r="D209" s="42"/>
       <c r="E209" s="39"/>
       <c r="F209" s="39"/>
-      <c r="G209" s="39"/>
-      <c r="H209" s="39"/>
-      <c r="I209" s="42"/>
-      <c r="J209" s="42"/>
-      <c r="K209" s="42"/>
+      <c r="G209" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H209" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="I209" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="J209" s="40"/>
+      <c r="K209" s="40"/>
     </row>
     <row r="210" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A210" s="51"/>
-      <c r="B210" s="52"/>
-      <c r="C210" s="53"/>
-      <c r="D210" s="53"/>
-      <c r="E210" s="51" t="s">
+      <c r="A210" s="39"/>
+      <c r="B210" s="39"/>
+      <c r="C210" s="39"/>
+      <c r="D210" s="39"/>
+      <c r="E210" s="39"/>
+      <c r="F210" s="39"/>
+      <c r="G210" s="39"/>
+      <c r="H210" s="39"/>
+      <c r="I210" s="40"/>
+      <c r="J210" s="40"/>
+      <c r="K210" s="40"/>
+    </row>
+    <row r="211" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211" s="51"/>
+      <c r="B211" s="52"/>
+      <c r="C211" s="53"/>
+      <c r="D211" s="53"/>
+      <c r="E211" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F210" s="51"/>
-      <c r="G210" s="51"/>
-      <c r="H210" s="51"/>
-      <c r="I210" s="54"/>
-      <c r="J210" s="54"/>
-      <c r="K210" s="54"/>
-    </row>
-    <row r="211" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A211" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="B211" s="44"/>
-      <c r="C211" s="45"/>
-      <c r="D211" s="45"/>
-      <c r="E211" s="43"/>
-      <c r="F211" s="43"/>
-      <c r="G211" s="43"/>
-      <c r="H211" s="43"/>
-      <c r="I211" s="46"/>
-      <c r="J211" s="46"/>
-      <c r="K211" s="46"/>
+      <c r="F211" s="51"/>
+      <c r="G211" s="51"/>
+      <c r="H211" s="51"/>
+      <c r="I211" s="54"/>
+      <c r="J211" s="54"/>
+      <c r="K211" s="54"/>
     </row>
     <row r="212" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A212" s="47"/>
-      <c r="B212" s="48"/>
-      <c r="C212" s="49"/>
-      <c r="D212" s="49"/>
-      <c r="E212" s="47" t="s">
+      <c r="A212" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="B212" s="44"/>
+      <c r="C212" s="45"/>
+      <c r="D212" s="45"/>
+      <c r="E212" s="43"/>
+      <c r="F212" s="43"/>
+      <c r="G212" s="43"/>
+      <c r="H212" s="43"/>
+      <c r="I212" s="46"/>
+      <c r="J212" s="46"/>
+      <c r="K212" s="46"/>
+    </row>
+    <row r="213" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A213" s="47"/>
+      <c r="B213" s="48"/>
+      <c r="C213" s="49"/>
+      <c r="D213" s="49"/>
+      <c r="E213" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F212" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="G212" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H212" s="47"/>
-      <c r="I212" s="50"/>
-      <c r="J212" s="50"/>
-      <c r="K212" s="50"/>
-    </row>
-    <row r="213" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A213" s="39"/>
-      <c r="B213" s="40"/>
-      <c r="C213" s="41"/>
-      <c r="D213" s="41"/>
-      <c r="E213" s="39"/>
-      <c r="F213" s="39"/>
-      <c r="G213" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H213" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="I213" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="J213" s="42"/>
-      <c r="K213" s="42"/>
+      <c r="F213" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="G213" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H213" s="47"/>
+      <c r="I213" s="50"/>
+      <c r="J213" s="50"/>
+      <c r="K213" s="50"/>
     </row>
     <row r="214" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="39"/>
-      <c r="B214" s="39"/>
-      <c r="C214" s="39"/>
-      <c r="D214" s="39"/>
+      <c r="B214" s="41"/>
+      <c r="C214" s="42"/>
+      <c r="D214" s="42"/>
       <c r="E214" s="39"/>
       <c r="F214" s="39"/>
-      <c r="G214" s="39"/>
-      <c r="H214" s="39"/>
-      <c r="I214" s="42"/>
-      <c r="J214" s="42"/>
-      <c r="K214" s="42"/>
+      <c r="G214" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H214" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="I214" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="J214" s="40"/>
+      <c r="K214" s="40"/>
     </row>
     <row r="215" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A215" s="51"/>
-      <c r="B215" s="52"/>
-      <c r="C215" s="53"/>
-      <c r="D215" s="53"/>
-      <c r="E215" s="51" t="s">
+      <c r="A215" s="39"/>
+      <c r="B215" s="39"/>
+      <c r="C215" s="39"/>
+      <c r="D215" s="39"/>
+      <c r="E215" s="39"/>
+      <c r="F215" s="39"/>
+      <c r="G215" s="39"/>
+      <c r="H215" s="39"/>
+      <c r="I215" s="40"/>
+      <c r="J215" s="40"/>
+      <c r="K215" s="40"/>
+    </row>
+    <row r="216" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" s="51"/>
+      <c r="B216" s="52"/>
+      <c r="C216" s="53"/>
+      <c r="D216" s="53"/>
+      <c r="E216" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F215" s="51"/>
-      <c r="G215" s="51"/>
-      <c r="H215" s="51"/>
-      <c r="I215" s="54"/>
-      <c r="J215" s="54"/>
-      <c r="K215" s="54"/>
-    </row>
-    <row r="216" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A216" s="43" t="s">
+      <c r="F216" s="51"/>
+      <c r="G216" s="51"/>
+      <c r="H216" s="51"/>
+      <c r="I216" s="54"/>
+      <c r="J216" s="54"/>
+      <c r="K216" s="54"/>
+    </row>
+    <row r="217" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A217" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B216" s="44"/>
-      <c r="C216" s="45"/>
-      <c r="D216" s="45"/>
-      <c r="E216" s="43"/>
-      <c r="F216" s="43"/>
-      <c r="G216" s="43"/>
-      <c r="H216" s="43"/>
-      <c r="I216" s="46"/>
-      <c r="J216" s="46"/>
-      <c r="K216" s="46"/>
-    </row>
-    <row r="217" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A217" s="47"/>
-      <c r="B217" s="48"/>
-      <c r="C217" s="49"/>
-      <c r="D217" s="49"/>
-      <c r="E217" s="47" t="s">
+      <c r="B217" s="44"/>
+      <c r="C217" s="45"/>
+      <c r="D217" s="45"/>
+      <c r="E217" s="43"/>
+      <c r="F217" s="43"/>
+      <c r="G217" s="43"/>
+      <c r="H217" s="43"/>
+      <c r="I217" s="46"/>
+      <c r="J217" s="46"/>
+      <c r="K217" s="46"/>
+    </row>
+    <row r="218" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A218" s="47"/>
+      <c r="B218" s="48"/>
+      <c r="C218" s="49"/>
+      <c r="D218" s="49"/>
+      <c r="E218" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F217" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="G217" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H217" s="47"/>
-      <c r="I217" s="50"/>
-      <c r="J217" s="50"/>
-      <c r="K217" s="50"/>
-    </row>
-    <row r="218" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A218" s="39"/>
-      <c r="B218" s="40"/>
-      <c r="C218" s="41"/>
-      <c r="D218" s="41"/>
-      <c r="E218" s="39"/>
-      <c r="F218" s="39"/>
-      <c r="G218" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H218" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="I218" s="42" t="s">
+      <c r="F218" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="G218" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H218" s="47"/>
+      <c r="I218" s="50"/>
+      <c r="J218" s="50"/>
+      <c r="K218" s="50"/>
+    </row>
+    <row r="219" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A219" s="39"/>
+      <c r="B219" s="41"/>
+      <c r="C219" s="42"/>
+      <c r="D219" s="42"/>
+      <c r="E219" s="39"/>
+      <c r="F219" s="39"/>
+      <c r="G219" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H219" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="J218" s="42" t="s">
+      <c r="I219" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="K218" s="42"/>
-    </row>
-    <row r="219" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A219" s="51"/>
-      <c r="B219" s="52"/>
-      <c r="C219" s="53"/>
-      <c r="D219" s="53"/>
-      <c r="E219" s="51" t="s">
+      <c r="J219" s="40" t="s">
         <v>209</v>
       </c>
-      <c r="F219" s="51" t="s">
+      <c r="K219" s="40"/>
+    </row>
+    <row r="220" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220" s="51"/>
+      <c r="B220" s="52"/>
+      <c r="C220" s="53"/>
+      <c r="D220" s="53"/>
+      <c r="E220" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="G219" s="51"/>
-      <c r="H219" s="51"/>
-      <c r="I219" s="54"/>
-      <c r="J219" s="54"/>
-      <c r="K219" s="54"/>
-    </row>
-    <row r="220" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A220" s="55"/>
-      <c r="B220" s="56"/>
-      <c r="C220" s="57"/>
-      <c r="D220" s="57"/>
-      <c r="E220" s="55" t="s">
+      <c r="F220" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="F220" s="55"/>
-      <c r="G220" s="55"/>
-      <c r="H220" s="55"/>
-      <c r="I220" s="58"/>
-      <c r="J220" s="58"/>
-      <c r="K220" s="58"/>
+      <c r="G220" s="51"/>
+      <c r="H220" s="51"/>
+      <c r="I220" s="54"/>
+      <c r="J220" s="54"/>
+      <c r="K220" s="54"/>
     </row>
     <row r="221" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A221" s="59"/>
-      <c r="B221" s="60"/>
-      <c r="C221" s="61"/>
-      <c r="D221" s="61"/>
-      <c r="E221" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="F221" s="59"/>
-      <c r="G221" s="59"/>
-      <c r="H221" s="59"/>
-      <c r="I221" s="62"/>
-      <c r="J221" s="62"/>
-      <c r="K221" s="62"/>
-    </row>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A221" s="55"/>
+      <c r="B221" s="56"/>
+      <c r="C221" s="57"/>
+      <c r="D221" s="57"/>
+      <c r="E221" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="F221" s="55"/>
+      <c r="G221" s="55"/>
+      <c r="H221" s="55"/>
+      <c r="I221" s="58"/>
+      <c r="J221" s="58"/>
+      <c r="K221" s="58"/>
+    </row>
+    <row r="222" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A222" s="59"/>
+      <c r="B222" s="60"/>
+      <c r="C222" s="61"/>
+      <c r="D222" s="61"/>
+      <c r="E222" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="F222" s="59"/>
+      <c r="G222" s="59"/>
+      <c r="H222" s="59"/>
+      <c r="I222" s="62"/>
+      <c r="J222" s="62"/>
+      <c r="K222" s="62"/>
+    </row>
     <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
